--- a/docs/testing/PROJECT TEST CASES CAA 131026.xlsx
+++ b/docs/testing/PROJECT TEST CASES CAA 131026.xlsx
@@ -10018,7 +10018,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>E06-S05 — Scenario 7 (Coordinator told before and at expiry); assumes O-33</t>
+          <t>E06-S05 — Scenario 7 (Coordinator told at expiry); T-92</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Verify that the Coordinator should receive a reminder 24 hours before a hold expires and a notice when it expires</t>
+          <t>Verify that the Coordinator should receive one notice when a hold expires and no reminder before it</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>Reminder at expiry minus 24h | Notice at expiry</t>
+          <t>No reminder at expiry minus 24h | One notice at expiry</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>After step 1 exactly one in-app notification and one email name "Riverside Hall", the event and the expiry time; after step 2 exactly one further notification and email say the hold has expired and the venue is free; step 3 produces nothing more</t>
+          <t>After step 1 there is no notification or email about the hold; after step 2 exactly one in-app notification and one email name "Riverside Hall", the event and the expiry time and say the hold has expired and the venue is free; step 3 produces nothing more</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>E06-S05 — Scenario 8 (Venue Staff may extend a hold); assumes O-34</t>
+          <t>E06-S05 — Scenario 8 (Venue Staff may extend a hold); T-92</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>Step 1 succeeds, the activity log records the extension by venue_staff_1, and the reminder is rescheduled to 06/01/2027 10:00; step 2 is refused with a message that an expired hold cannot be extended and must be placed again
+          <t>Step 1 succeeds and the activity log records the extension by venue_staff_1 with the old and new expiry; step 2 is refused with a message that an expired hold cannot be extended and must be placed again
 ## E06-S06</t>
         </is>
       </c>
